--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-pss4-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-pss4-score-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4000" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4000" uniqueCount="607">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1518,6 +1518,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -8435,7 +8439,7 @@
         <v>480</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>481</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
@@ -8444,10 +8448,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8458,10 +8462,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8487,10 +8491,10 @@
         <v>477</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8541,7 +8545,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8553,7 +8557,7 @@
         <v>480</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>481</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8562,10 +8566,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8576,10 +8580,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8605,16 +8609,16 @@
         <v>182</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8642,10 +8646,10 @@
         <v>117</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8663,7 +8667,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8681,10 +8685,10 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>414</v>
@@ -8698,10 +8702,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8727,16 +8731,16 @@
         <v>182</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8764,10 +8768,10 @@
         <v>270</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8785,7 +8789,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8803,10 +8807,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>414</v>
@@ -8820,10 +8824,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8846,17 +8850,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8905,7 +8909,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8929,7 +8933,7 @@
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8940,10 +8944,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8969,10 +8973,10 @@
         <v>160</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9023,7 +9027,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9044,10 +9048,10 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -9058,10 +9062,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9084,16 +9088,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9143,7 +9147,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9164,10 +9168,10 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -9178,10 +9182,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9204,16 +9208,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9263,7 +9267,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9284,10 +9288,10 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -9298,10 +9302,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9309,10 +9313,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -9327,16 +9331,16 @@
         <v>461</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9373,7 +9377,7 @@
         <v>21</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
@@ -9383,7 +9387,7 @@
         <v>314</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9404,10 +9408,10 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -9418,10 +9422,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9536,10 +9540,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9656,10 +9660,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9778,10 +9782,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9807,13 +9811,13 @@
         <v>182</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>268</v>
@@ -9865,7 +9869,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>93</v>
@@ -9883,7 +9887,7 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>275</v>
@@ -9900,10 +9904,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9926,16 +9930,16 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M64" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>344</v>
@@ -9987,7 +9991,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10005,7 +10009,7 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>347</v>
@@ -10022,10 +10026,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10051,13 +10055,13 @@
         <v>182</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>399</v>
@@ -10109,7 +10113,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10144,10 +10148,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10231,7 +10235,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10266,10 +10270,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10295,10 +10299,10 @@
         <v>21</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>464</v>
@@ -10353,7 +10357,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10388,13 +10392,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>21</v>
@@ -10419,16 +10423,16 @@
         <v>461</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10477,7 +10481,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10498,10 +10502,10 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>21</v>
@@ -10512,10 +10516,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10630,10 +10634,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10750,10 +10754,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10872,10 +10876,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10901,13 +10905,13 @@
         <v>182</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>268</v>
@@ -10920,7 +10924,7 @@
         <v>21</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>21</v>
@@ -10959,7 +10963,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>93</v>
@@ -10977,7 +10981,7 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>275</v>
@@ -10994,10 +10998,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11023,13 +11027,13 @@
         <v>182</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>344</v>
@@ -11061,7 +11065,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -11079,7 +11083,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11097,7 +11101,7 @@
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>347</v>
@@ -11114,10 +11118,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11143,13 +11147,13 @@
         <v>182</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>399</v>
@@ -11201,7 +11205,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11236,10 +11240,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11323,7 +11327,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11358,10 +11362,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11387,10 +11391,10 @@
         <v>83</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>464</v>
@@ -11445,7 +11449,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11480,13 +11484,13 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>21</v>
@@ -11511,16 +11515,16 @@
         <v>461</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -11569,7 +11573,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11590,10 +11594,10 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>21</v>
@@ -11604,10 +11608,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11722,10 +11726,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11842,10 +11846,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11964,10 +11968,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11993,13 +11997,13 @@
         <v>182</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>268</v>
@@ -12012,7 +12016,7 @@
         <v>21</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>21</v>
@@ -12051,7 +12055,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>93</v>
@@ -12069,7 +12073,7 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>275</v>
@@ -12086,10 +12090,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12115,13 +12119,13 @@
         <v>182</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M82" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O82" t="s" s="2">
         <v>344</v>
@@ -12153,7 +12157,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>21</v>
@@ -12171,7 +12175,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12189,7 +12193,7 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>347</v>
@@ -12206,10 +12210,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12235,13 +12239,13 @@
         <v>182</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>399</v>
@@ -12293,7 +12297,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12328,10 +12332,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12415,7 +12419,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12450,10 +12454,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12479,10 +12483,10 @@
         <v>83</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>464</v>
@@ -12537,7 +12541,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12572,13 +12576,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>21</v>
@@ -12603,16 +12607,16 @@
         <v>461</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -12661,7 +12665,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12682,10 +12686,10 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>21</v>
@@ -12696,10 +12700,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12814,10 +12818,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12934,10 +12938,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13056,10 +13060,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13085,13 +13089,13 @@
         <v>182</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>268</v>
@@ -13104,7 +13108,7 @@
         <v>21</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>21</v>
@@ -13143,7 +13147,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>93</v>
@@ -13161,7 +13165,7 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>275</v>
@@ -13178,10 +13182,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13207,13 +13211,13 @@
         <v>182</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M91" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>344</v>
@@ -13245,7 +13249,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>21</v>
@@ -13263,7 +13267,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13281,7 +13285,7 @@
         <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>347</v>
@@ -13298,10 +13302,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13327,13 +13331,13 @@
         <v>182</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>399</v>
@@ -13385,7 +13389,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13420,10 +13424,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13507,7 +13511,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13542,10 +13546,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13571,10 +13575,10 @@
         <v>83</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>464</v>
@@ -13629,7 +13633,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13664,13 +13668,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>21</v>
@@ -13695,16 +13699,16 @@
         <v>461</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
@@ -13753,7 +13757,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13774,10 +13778,10 @@
         <v>21</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>21</v>
@@ -13788,10 +13792,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13906,10 +13910,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14026,10 +14030,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14148,10 +14152,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14177,13 +14181,13 @@
         <v>182</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O99" t="s" s="2">
         <v>268</v>
@@ -14196,7 +14200,7 @@
         <v>21</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>21</v>
@@ -14235,7 +14239,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>93</v>
@@ -14253,7 +14257,7 @@
         <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>275</v>
@@ -14270,10 +14274,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14299,13 +14303,13 @@
         <v>182</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>344</v>
@@ -14337,7 +14341,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>21</v>
@@ -14355,7 +14359,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14373,7 +14377,7 @@
         <v>21</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>347</v>
@@ -14390,10 +14394,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14419,13 +14423,13 @@
         <v>182</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>399</v>
@@ -14477,7 +14481,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14512,10 +14516,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14599,7 +14603,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14634,10 +14638,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14663,10 +14667,10 @@
         <v>83</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>464</v>
@@ -14721,7 +14725,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
